--- a/data/WP17_auswertung_parteien.xlsx
+++ b/data/WP17_auswertung_parteien.xlsx
@@ -686,13 +686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B8D1AF8-A5E0-4912-A2BE-B7542291054D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92D3402F-0778-4177-99B1-9482929D6B70}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B66329B9-80AA-4628-A6E5-7D3149ECDE5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5FB835A-1D2D-4A7A-8427-40D1DC7B27E2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A74F42CB-BCBA-405C-BE89-C9BCC3F86C6D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8189CC15-1669-456E-965C-7A787CC99D5B}"/>
 </file>